--- a/Team-Data/2007-08/4-2-2007-08.xlsx
+++ b/Team-Data/2007-08/4-2-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>0.467</v>
+        <v>0.459</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.359</v>
+        <v>0.354</v>
       </c>
       <c r="O2" t="n">
         <v>21.1</v>
@@ -700,19 +767,19 @@
         <v>27.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R2" t="n">
         <v>12.3</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T2" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
@@ -727,19 +794,19 @@
         <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA2" t="n">
         <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,13 +818,13 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>16</v>
@@ -769,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
@@ -790,16 +857,16 @@
         <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
         <v>24</v>
@@ -808,10 +875,10 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -870,13 +937,13 @@
         <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="P3" t="n">
         <v>26.6</v>
@@ -888,16 +955,16 @@
         <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
@@ -915,13 +982,13 @@
         <v>22.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>19</v>
@@ -951,10 +1018,10 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
         <v>9</v>
@@ -984,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -993,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>0.373</v>
+        <v>0.378</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
         <v>79.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -1058,10 +1125,10 @@
         <v>0.366</v>
       </c>
       <c r="O4" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P4" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0.71</v>
@@ -1097,13 +1164,13 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="n">
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1118,13 +1185,13 @@
         <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1139,7 +1206,7 @@
         <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
@@ -1154,7 +1221,7 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
@@ -1169,13 +1236,13 @@
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1312,13 +1379,13 @@
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN5" t="n">
         <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
@@ -1336,13 +1403,13 @@
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1354,7 +1421,7 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J6" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R6" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
         <v>44.4</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W6" t="n">
         <v>7.1</v>
@@ -1461,13 +1528,13 @@
         <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,19 +1549,19 @@
         <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN6" t="n">
         <v>15</v>
@@ -1509,10 +1576,10 @@
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
@@ -1530,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
@@ -1539,7 +1606,7 @@
         <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.627</v>
+        <v>0.622</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
         <v>0.464</v>
@@ -1604,25 +1671,25 @@
         <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P7" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S7" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T7" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="V7" t="n">
         <v>13.1</v>
@@ -1637,31 +1704,31 @@
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1679,16 +1746,16 @@
         <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>21</v>
@@ -1697,25 +1764,25 @@
         <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>21</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
@@ -1843,25 +1910,25 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,7 +2098,7 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
@@ -2040,10 +2107,10 @@
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>18</v>
@@ -2052,7 +2119,7 @@
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2064,16 +2131,16 @@
         <v>23</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6</v>
+        <v>0.608</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="J10" t="n">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M10" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R10" t="n">
         <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U10" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="V10" t="n">
         <v>13.1</v>
@@ -2183,25 +2250,25 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.5</v>
+        <v>110.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
@@ -2225,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -2240,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2392,25 +2459,25 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
         <v>18</v>
       </c>
       <c r="AL11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2419,10 +2486,10 @@
         <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
@@ -2449,7 +2516,7 @@
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -2481,67 +2548,67 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
         <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.413</v>
+        <v>0.419</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L12" t="n">
         <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O12" t="n">
         <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.769</v>
+        <v>0.772</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
         <v>31.9</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
         <v>7.7</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="n">
         <v>5.2</v>
@@ -2550,16 +2617,16 @@
         <v>23.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.7</v>
+        <v>104</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2577,10 +2644,10 @@
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2607,13 +2674,13 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>0.307</v>
+        <v>0.297</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,43 +2748,43 @@
         <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.439</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.324</v>
+        <v>0.322</v>
       </c>
       <c r="O13" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P13" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R13" t="n">
         <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T13" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2729,19 +2796,19 @@
         <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2786,7 +2853,7 @@
         <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
         <v>29</v>
@@ -2795,13 +2862,13 @@
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
@@ -2810,13 +2877,13 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.475</v>
@@ -2872,31 +2939,31 @@
         <v>7.9</v>
       </c>
       <c r="M14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
         <v>21.2</v>
       </c>
       <c r="P14" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R14" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S14" t="n">
         <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V14" t="n">
         <v>14.2</v>
@@ -2905,10 +2972,10 @@
         <v>8</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
         <v>20.7</v>
@@ -2917,13 +2984,13 @@
         <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.4</v>
+        <v>108.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2950,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN14" t="n">
         <v>8</v>
@@ -2962,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
@@ -2989,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3094,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
         <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>0.267</v>
+        <v>0.257</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M15" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O15" t="n">
         <v>18.5</v>
@@ -3069,10 +3136,10 @@
         <v>0.729</v>
       </c>
       <c r="R15" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S15" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T15" t="n">
         <v>41.5</v>
@@ -3081,7 +3148,7 @@
         <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W15" t="n">
         <v>6.1</v>
@@ -3093,49 +3160,49 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.6</v>
+        <v>100.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>13</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>14</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3150,10 +3217,10 @@
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3162,10 +3229,10 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>18</v>
@@ -3174,10 +3241,10 @@
         <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>0.173</v>
+        <v>0.176</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J16" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L16" t="n">
         <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O16" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R16" t="n">
         <v>9.1</v>
@@ -3266,13 +3333,13 @@
         <v>14.9</v>
       </c>
       <c r="W16" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="n">
         <v>20.4</v>
@@ -3281,13 +3348,13 @@
         <v>20.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>91.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI16" t="n">
         <v>29</v>
@@ -3308,16 +3375,16 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN16" t="n">
         <v>23</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3338,13 +3405,13 @@
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
         <v>23</v>
       </c>
       <c r="AW16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
         <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>0.351</v>
+        <v>0.342</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
@@ -3424,13 +3491,13 @@
         <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.736</v>
+        <v>0.738</v>
       </c>
       <c r="R17" t="n">
         <v>12.9</v>
@@ -3442,7 +3509,7 @@
         <v>41.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V17" t="n">
         <v>14.5</v>
@@ -3457,19 +3524,19 @@
         <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3481,22 +3548,22 @@
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN17" t="n">
         <v>25</v>
@@ -3508,7 +3575,7 @@
         <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
@@ -3517,19 +3584,19 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU17" t="n">
         <v>18</v>
       </c>
-      <c r="AU17" t="n">
-        <v>16</v>
-      </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>22</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>20</v>
@@ -3544,7 +3611,7 @@
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>0.257</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3591,37 +3658,37 @@
         <v>37</v>
       </c>
       <c r="J18" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R18" t="n">
         <v>11.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>19.9</v>
@@ -3630,7 +3697,7 @@
         <v>14.8</v>
       </c>
       <c r="W18" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X18" t="n">
         <v>3.8</v>
@@ -3645,22 +3712,22 @@
         <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF18" t="n">
         <v>26</v>
       </c>
       <c r="AG18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH18" t="n">
         <v>29</v>
@@ -3690,16 +3757,16 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
@@ -3726,7 +3793,7 @@
         <v>28</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
@@ -3854,7 +3921,7 @@
         <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>18</v>
@@ -3863,7 +3930,7 @@
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3887,13 +3954,13 @@
         <v>6</v>
       </c>
       <c r="AV19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW19" t="n">
         <v>25</v>
       </c>
-      <c r="AW19" t="n">
-        <v>26</v>
-      </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.703</v>
+        <v>0.699</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,7 +4022,7 @@
         <v>38.5</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
         <v>0.464</v>
@@ -3967,7 +4034,7 @@
         <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="O20" t="n">
         <v>15.9</v>
@@ -3976,22 +4043,22 @@
         <v>20.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R20" t="n">
         <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W20" t="n">
         <v>7.6</v>
@@ -4009,16 +4076,16 @@
         <v>19.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>3</v>
@@ -4027,7 +4094,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4054,16 +4121,16 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>13</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J21" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K21" t="n">
         <v>0.438</v>
       </c>
       <c r="L21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M21" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O21" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.723</v>
+        <v>0.722</v>
       </c>
       <c r="R21" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U21" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
         <v>6.3</v>
@@ -4182,7 +4249,7 @@
         <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
         <v>21.4</v>
@@ -4191,13 +4258,13 @@
         <v>20.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4212,10 +4279,10 @@
         <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
         <v>29</v>
@@ -4224,7 +4291,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN21" t="n">
         <v>28</v>
@@ -4239,10 +4306,10 @@
         <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4251,16 +4318,16 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4391,7 +4458,7 @@
         <v>9</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
         <v>12</v>
@@ -4412,7 +4479,7 @@
         <v>4</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
         <v>3</v>
@@ -4448,7 +4515,7 @@
         <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -4561,19 +4628,19 @@
         <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>14</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4603,13 +4670,13 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
@@ -4633,7 +4700,7 @@
         <v>16</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>6</v>
@@ -4755,7 +4822,7 @@
         <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4764,7 +4831,7 @@
         <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>4</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
         <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4868,22 +4935,22 @@
         <v>79.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M25" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="O25" t="n">
         <v>17.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="O25" t="n">
-        <v>17.4</v>
-      </c>
       <c r="P25" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0.769</v>
@@ -4913,7 +4980,7 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
         <v>20.4</v>
@@ -4922,10 +4989,10 @@
         <v>95.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4940,13 +5007,13 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4964,28 +5031,28 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
         <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -5107,25 +5174,25 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="n">
         <v>10</v>
@@ -5134,7 +5201,7 @@
         <v>17</v>
       </c>
       <c r="AM26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN26" t="n">
         <v>12</v>
@@ -5164,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -5301,10 +5368,10 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>26</v>
@@ -5319,7 +5386,7 @@
         <v>8</v>
       </c>
       <c r="AN27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>25</v>
@@ -5361,7 +5428,7 @@
         <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
         <v>5</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>0.227</v>
+        <v>0.23</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,10 +5478,10 @@
         <v>38.1</v>
       </c>
       <c r="J28" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L28" t="n">
         <v>4</v>
@@ -5423,7 +5490,7 @@
         <v>11.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.336</v>
+        <v>0.339</v>
       </c>
       <c r="O28" t="n">
         <v>17.5</v>
@@ -5432,7 +5499,7 @@
         <v>22.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
         <v>11.8</v>
@@ -5441,13 +5508,13 @@
         <v>32.6</v>
       </c>
       <c r="T28" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="U28" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V28" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
@@ -5465,13 +5532,13 @@
         <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5501,7 +5568,7 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO28" t="n">
         <v>23</v>
@@ -5531,7 +5598,7 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5543,7 +5610,7 @@
         <v>27</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" t="n">
         <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J29" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L29" t="n">
         <v>7.2</v>
@@ -5614,19 +5681,19 @@
         <v>20.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R29" t="n">
         <v>9.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V29" t="n">
         <v>11.8</v>
@@ -5638,7 +5705,7 @@
         <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z29" t="n">
         <v>19.6</v>
@@ -5647,13 +5714,13 @@
         <v>18.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.4</v>
+        <v>100.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5674,7 +5741,7 @@
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL29" t="n">
         <v>10</v>
@@ -5686,19 +5753,19 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP29" t="n">
         <v>30</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR29" t="n">
         <v>27</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5719,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.658</v>
+        <v>0.653</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,31 +5842,31 @@
         <v>40.2</v>
       </c>
       <c r="J30" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>0.499</v>
       </c>
       <c r="L30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="N30" t="n">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="Q30" t="n">
         <v>0.758</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
         <v>29.1</v>
@@ -5820,7 +5887,7 @@
         <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z30" t="n">
         <v>24.3</v>
@@ -5829,16 +5896,16 @@
         <v>23.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>107.1</v>
+        <v>107</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
         <v>38</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L31" t="n">
         <v>6.8</v>
@@ -5969,7 +6036,7 @@
         <v>19.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O31" t="n">
         <v>19.2</v>
@@ -5978,16 +6045,16 @@
         <v>24.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S31" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T31" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U31" t="n">
         <v>19.4</v>
@@ -5996,7 +6063,7 @@
         <v>13.2</v>
       </c>
       <c r="W31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
         <v>4.9</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6035,7 +6102,7 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6047,7 +6114,7 @@
         <v>10</v>
       </c>
       <c r="AN31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6074,13 +6141,13 @@
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
         <v>6</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-2-2007-08</t>
+          <t>2008-04-02</t>
         </is>
       </c>
     </row>
